--- a/Relatório 2/Scripts_Controle_Qualidade/Resultados/qc_serie_anual_nacional.xlsx
+++ b/Relatório 2/Scripts_Controle_Qualidade/Resultados/qc_serie_anual_nacional.xlsx
@@ -5,30 +5,17 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rhamars-my.sharepoint.com/personal/daniele_silva_rhama_com_br/Documents/Área de Trabalho/UNB/R/UNIPLU/02a. QC_diarios_anual/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rhamars-my.sharepoint.com/personal/daniele_silva_rhama_com_br/Documents/Área de Trabalho/UNB/R/UNIPLU/02. QC_diarios_anual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_32A53EDD8F79A8D366075C52F37BD2724AC507D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B6A1F0A-9CB6-4F94-BE14-E72298D13869}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_F3AC3EDD8F79A8D366075C52F37BD2729A4B2727" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{829A1ADC-6C11-4BED-89AA-65A3B5A794C2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -408,6 +395,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
